--- a/4_tables/2_meta_analysis/meta_housing_ma_treatment_group.xlsx
+++ b/4_tables/2_meta_analysis/meta_housing_ma_treatment_group.xlsx
@@ -412,12 +412,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.796 [0.713, 0.889]</t>
+          <t>0.771 [0.722, 0.823]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
     </row>
@@ -444,12 +444,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.960 [0.885, 1.041]</t>
+          <t>0.986 [0.933, 1.042]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.943 [0.885, 1.005]</t>
+          <t>0.987 [0.943, 1.033]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.813 [0.651, 1.015]</t>
+          <t>0.819 [0.709, 0.947]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
     </row>
@@ -540,12 +540,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.989 [0.969, 1.009]</t>
+          <t>0.998 [0.979, 1.016]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.941 [0.913, 0.971]</t>
+          <t>1.011 [0.975, 1.049]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.957 [0.935, 0.979]</t>
+          <t>0.984 [0.963, 1.007]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1244,90 +1244,125 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>bc_estimate</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>pet_status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>peese_status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fit_status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>fit_note</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pet_term</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>model_formula</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>estimate_rr</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>std_error</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>statistic</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>conf_low</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>conf_high</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>conf_low_rr</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>conf_high_rr</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>pet_term_estimate</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pet_term_p_value</t>
         </is>
@@ -1367,74 +1402,94 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J2">
+        <v>-0.2280248923827685</v>
+      </c>
+      <c r="K2">
+        <v>0.05623988471185582</v>
+      </c>
+      <c r="L2">
+        <v>-4.054504975446704</v>
+      </c>
+      <c r="M2">
+        <v>5.02405812419616E-05</v>
+      </c>
+      <c r="N2">
+        <v>0.1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q2">
         <v>0.1061267217701378</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>prratio_ln_se</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
-        </is>
-      </c>
-      <c r="Q2">
-        <v>-0.2280248923827685</v>
-      </c>
-      <c r="R2">
-        <v>0.7961044426522961</v>
-      </c>
-      <c r="S2">
-        <v>0.05623988514012759</v>
-      </c>
-      <c r="T2">
-        <v>-4.054504944571285</v>
-      </c>
-      <c r="U2">
-        <v>0.0001687235753945533</v>
-      </c>
-      <c r="V2">
-        <v>-0.3382530417520879</v>
-      </c>
-      <c r="W2">
-        <v>-0.117796743013449</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>prratio_ln_v</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
+        </is>
       </c>
       <c r="X2">
-        <v>0.7130148425441187</v>
+        <v>-0.2598660612944457</v>
       </c>
       <c r="Y2">
-        <v>0.8888767046550042</v>
+        <v>0.7711548663713628</v>
       </c>
       <c r="Z2">
-        <v>-1.018234177038682</v>
+        <v>0.03328198001093026</v>
       </c>
       <c r="AA2">
-        <v>0.1061267217701378</v>
+        <v>-7.80801085780059</v>
+      </c>
+      <c r="AB2">
+        <v>2.562752350564518E-10</v>
+      </c>
+      <c r="AC2">
+        <v>-0.3250975434500509</v>
+      </c>
+      <c r="AD2">
+        <v>-0.1946345791388404</v>
+      </c>
+      <c r="AE2">
+        <v>0.7224568792684545</v>
+      </c>
+      <c r="AF2">
+        <v>0.8231353939495953</v>
+      </c>
+      <c r="AG2">
+        <v>-4.931118471925302</v>
+      </c>
+      <c r="AH2">
+        <v>0.01784479789143678</v>
       </c>
     </row>
     <row r="3">
@@ -1471,74 +1526,94 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J3">
+        <v>-0.01398931214936958</v>
+      </c>
+      <c r="K3">
+        <v>0.02801957205396191</v>
+      </c>
+      <c r="L3">
+        <v>-0.4992693008454251</v>
+      </c>
+      <c r="M3">
+        <v>0.6175896790784481</v>
+      </c>
+      <c r="N3">
+        <v>0.1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q3">
         <v>0.06140889364563524</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q3">
-        <v>-0.04104926192869048</v>
-      </c>
-      <c r="R3">
-        <v>0.959781848078252</v>
-      </c>
-      <c r="S3">
-        <v>0.0414834596191135</v>
-      </c>
-      <c r="T3">
-        <v>-0.9895332333800104</v>
-      </c>
-      <c r="U3">
-        <v>0.3457406751163927</v>
-      </c>
-      <c r="V3">
-        <v>-0.1223553487362746</v>
-      </c>
-      <c r="W3">
-        <v>0.04025682487889364</v>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X3">
-        <v>0.8848338880268932</v>
+        <v>-0.01398931214936958</v>
       </c>
       <c r="Y3">
-        <v>1.041078114621789</v>
+        <v>0.9861080835824433</v>
       </c>
       <c r="Z3">
-        <v>-4.988835520931911</v>
+        <v>0.02801957213560818</v>
       </c>
       <c r="AA3">
-        <v>0.04171936190697131</v>
+        <v>-0.4992692993906037</v>
+      </c>
+      <c r="AB3">
+        <v>0.6283901339179836</v>
+      </c>
+      <c r="AC3">
+        <v>-0.06890666439738365</v>
+      </c>
+      <c r="AD3">
+        <v>0.04092804009864449</v>
+      </c>
+      <c r="AE3">
+        <v>0.9334137967518054</v>
+      </c>
+      <c r="AF3">
+        <v>1.041777136668146</v>
+      </c>
+      <c r="AG3">
+        <v>-1.438915400305928</v>
+      </c>
+      <c r="AH3">
+        <v>0.06140889364563524</v>
       </c>
     </row>
     <row r="4">
@@ -1575,74 +1650,94 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J4">
+        <v>-0.01300522048704099</v>
+      </c>
+      <c r="K4">
+        <v>0.02317731125588256</v>
+      </c>
+      <c r="L4">
+        <v>-0.5611186018714822</v>
+      </c>
+      <c r="M4">
+        <v>0.5747166878669911</v>
+      </c>
+      <c r="N4">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q4">
         <v>3.648344743013438E-07</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q4">
-        <v>-0.05867009048934309</v>
-      </c>
-      <c r="R4">
-        <v>0.9430178283938843</v>
-      </c>
-      <c r="S4">
-        <v>0.03259294229560664</v>
-      </c>
-      <c r="T4">
-        <v>-1.800085735041219</v>
-      </c>
-      <c r="U4">
-        <v>0.08158614487495558</v>
-      </c>
-      <c r="V4">
-        <v>-0.1225510835389243</v>
-      </c>
-      <c r="W4">
-        <v>0.00521090256023813</v>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X4">
-        <v>0.8846607121892646</v>
+        <v>-0.01300522048704099</v>
       </c>
       <c r="Y4">
-        <v>1.005224502926116</v>
+        <v>0.9870789819738031</v>
       </c>
       <c r="Z4">
-        <v>-13.28632606558108</v>
+        <v>0.0231773111185831</v>
       </c>
       <c r="AA4">
-        <v>0.0003475644117808953</v>
+        <v>-0.5611186051954777</v>
+      </c>
+      <c r="AB4">
+        <v>0.578750576522196</v>
+      </c>
+      <c r="AC4">
+        <v>-0.05843191553794361</v>
+      </c>
+      <c r="AD4">
+        <v>0.03242147456386164</v>
+      </c>
+      <c r="AE4">
+        <v>0.9432424583688857</v>
+      </c>
+      <c r="AF4">
+        <v>1.032952776891854</v>
+      </c>
+      <c r="AG4">
+        <v>-2.634695400220785</v>
+      </c>
+      <c r="AH4">
+        <v>3.648344743013438E-07</v>
       </c>
     </row>
     <row r="5">
@@ -1679,74 +1774,94 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J5">
+        <v>-0.2071747835899547</v>
+      </c>
+      <c r="K5">
+        <v>0.1133988387623222</v>
+      </c>
+      <c r="L5">
+        <v>-1.826956835282783</v>
+      </c>
+      <c r="M5">
+        <v>0.0677062596835441</v>
+      </c>
+      <c r="N5">
+        <v>0.1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q5">
         <v>0.8755791713346561</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>prratio_ln_se</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
-        </is>
-      </c>
-      <c r="Q5">
-        <v>-0.2071747835899547</v>
-      </c>
-      <c r="R5">
-        <v>0.8128775599123109</v>
-      </c>
-      <c r="S5">
-        <v>0.1133988387718463</v>
-      </c>
-      <c r="T5">
-        <v>-1.826956835129341</v>
-      </c>
-      <c r="U5">
-        <v>0.08130569386996259</v>
-      </c>
-      <c r="V5">
-        <v>-0.4294324234714377</v>
-      </c>
-      <c r="W5">
-        <v>0.01508285629152831</v>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>prratio_ln_v</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
+        </is>
       </c>
       <c r="X5">
-        <v>0.6508784132154372</v>
+        <v>-0.1992084125040391</v>
       </c>
       <c r="Y5">
-        <v>1.015197176604291</v>
+        <v>0.8193791066851257</v>
       </c>
       <c r="Z5">
-        <v>0.1876542705546367</v>
+        <v>0.07392677096711239</v>
       </c>
       <c r="AA5">
-        <v>0.8755791713346561</v>
+        <v>-2.694672172177796</v>
+      </c>
+      <c r="AB5">
+        <v>0.01323585520137345</v>
+      </c>
+      <c r="AC5">
+        <v>-0.3441022210929207</v>
+      </c>
+      <c r="AD5">
+        <v>-0.05431460391515758</v>
+      </c>
+      <c r="AE5">
+        <v>0.7088564642634092</v>
+      </c>
+      <c r="AF5">
+        <v>0.9471340875331721</v>
+      </c>
+      <c r="AG5">
+        <v>-0.1863456442543887</v>
+      </c>
+      <c r="AH5">
+        <v>0.8903727859390478</v>
       </c>
     </row>
     <row r="6">
@@ -1783,74 +1898,94 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J6">
+        <v>-0.002326701182641406</v>
+      </c>
+      <c r="K6">
+        <v>0.009419121958906233</v>
+      </c>
+      <c r="L6">
+        <v>-0.2470189039692174</v>
+      </c>
+      <c r="M6">
+        <v>0.8048935940809889</v>
+      </c>
+      <c r="N6">
+        <v>0.1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q6">
         <v>0.05791197033513358</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q6">
-        <v>-0.01135694937232996</v>
-      </c>
-      <c r="R6">
-        <v>0.9887072973316636</v>
-      </c>
-      <c r="S6">
-        <v>0.01021621409258023</v>
-      </c>
-      <c r="T6">
-        <v>-1.111659296625177</v>
-      </c>
-      <c r="U6">
-        <v>0.2880608845387202</v>
-      </c>
-      <c r="V6">
-        <v>-0.03138036105213775</v>
-      </c>
-      <c r="W6">
-        <v>0.008666462307477833</v>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X6">
-        <v>0.9691068924473497</v>
+        <v>-0.002326701182641406</v>
       </c>
       <c r="Y6">
-        <v>1.00870412481355</v>
+        <v>0.9976760034884947</v>
       </c>
       <c r="Z6">
-        <v>-8.037711675485626</v>
+        <v>0.009419121996543186</v>
       </c>
       <c r="AA6">
-        <v>0.02518683488334981</v>
+        <v>-0.2470189029821786</v>
+      </c>
+      <c r="AB6">
+        <v>0.8090690395779558</v>
+      </c>
+      <c r="AC6">
+        <v>-0.02078784106185505</v>
+      </c>
+      <c r="AD6">
+        <v>0.01613443869657224</v>
+      </c>
+      <c r="AE6">
+        <v>0.9794267366647682</v>
+      </c>
+      <c r="AF6">
+        <v>1.016265301605157</v>
+      </c>
+      <c r="AG6">
+        <v>-0.948379600560244</v>
+      </c>
+      <c r="AH6">
+        <v>0.05791197033513358</v>
       </c>
     </row>
     <row r="7">
@@ -1887,74 +2022,94 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J7">
+        <v>0.01125249478786305</v>
+      </c>
+      <c r="K7">
+        <v>0.01867213013725901</v>
+      </c>
+      <c r="L7">
+        <v>0.6026358377510148</v>
+      </c>
+      <c r="M7">
+        <v>0.5467509738989856</v>
+      </c>
+      <c r="N7">
+        <v>0.1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q7">
         <v>0.001963325122337626</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q7">
-        <v>-0.06033396056904067</v>
-      </c>
-      <c r="R7">
-        <v>0.9414500738762047</v>
-      </c>
-      <c r="S7">
-        <v>0.01552697325646305</v>
-      </c>
-      <c r="T7">
-        <v>-3.885751561008637</v>
-      </c>
-      <c r="U7">
-        <v>0.002165206649137497</v>
-      </c>
-      <c r="V7">
-        <v>-0.09076626894062485</v>
-      </c>
-      <c r="W7">
-        <v>-0.0299016521974565</v>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X7">
-        <v>0.9132311364371795</v>
+        <v>0.01125249478786305</v>
       </c>
       <c r="Y7">
-        <v>0.9705409794275901</v>
+        <v>1.011316042239452</v>
       </c>
       <c r="Z7">
-        <v>-14.15774432702603</v>
+        <v>0.01867213018063969</v>
       </c>
       <c r="AA7">
-        <v>0.02523944556753687</v>
+        <v>0.6026358363509199</v>
+      </c>
+      <c r="AB7">
+        <v>0.5579679180388102</v>
+      </c>
+      <c r="AC7">
+        <v>-0.02534420788083411</v>
+      </c>
+      <c r="AD7">
+        <v>0.04784919745656022</v>
+      </c>
+      <c r="AE7">
+        <v>0.9749742604406317</v>
+      </c>
+      <c r="AF7">
+        <v>1.049012449650354</v>
+      </c>
+      <c r="AG7">
+        <v>-2.976198166772118</v>
+      </c>
+      <c r="AH7">
+        <v>0.001963325122337626</v>
       </c>
     </row>
     <row r="8">
@@ -2000,64 +2155,84 @@
         </is>
       </c>
       <c r="J8">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="K8">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="L8">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="M8">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="N8">
+        <v>0.1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q8">
         <v>0.6896331316971431</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q8">
+      <c r="X8">
         <v>0.01886571046568258</v>
       </c>
-      <c r="R8">
+      <c r="Y8">
         <v>1.019044792377816</v>
       </c>
-      <c r="S8">
+      <c r="Z8">
         <v>0.04777190240922339</v>
       </c>
-      <c r="T8">
+      <c r="AA8">
         <v>0.3949122709009</v>
       </c>
-      <c r="U8">
+      <c r="AB8">
         <v>0.6960102049424469</v>
       </c>
-      <c r="V8">
+      <c r="AC8">
         <v>-0.07476549772935748</v>
       </c>
-      <c r="W8">
+      <c r="AD8">
         <v>0.1124969186607226</v>
       </c>
-      <c r="X8">
+      <c r="AE8">
         <v>0.9279610697935819</v>
       </c>
-      <c r="Y8">
+      <c r="AF8">
         <v>1.119068808676794</v>
       </c>
-      <c r="Z8">
+      <c r="AG8">
         <v>0.2119180839801686</v>
       </c>
-      <c r="AA8">
+      <c r="AH8">
         <v>0.6896331316971431</v>
       </c>
     </row>
@@ -2095,74 +2270,94 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J9">
+        <v>-0.01562270818073927</v>
+      </c>
+      <c r="K9">
+        <v>0.01140561087549029</v>
+      </c>
+      <c r="L9">
+        <v>-1.369738837427039</v>
+      </c>
+      <c r="M9">
+        <v>0.1707684405789152</v>
+      </c>
+      <c r="N9">
+        <v>0.1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q9">
         <v>0.009018500526151949</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q9">
-        <v>-0.04417121364231996</v>
-      </c>
-      <c r="R9">
-        <v>0.9567901279257822</v>
-      </c>
-      <c r="S9">
-        <v>0.01182664939555682</v>
-      </c>
-      <c r="T9">
-        <v>-3.734888231227583</v>
-      </c>
-      <c r="U9">
-        <v>0.003295332952781328</v>
-      </c>
-      <c r="V9">
-        <v>-0.06735102051539371</v>
-      </c>
-      <c r="W9">
-        <v>-0.02099140676924621</v>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X9">
-        <v>0.9348669862436952</v>
+        <v>-0.01562270818073927</v>
       </c>
       <c r="Y9">
-        <v>0.9792273792601353</v>
+        <v>0.9844986932958903</v>
       </c>
       <c r="Z9">
-        <v>-9.163029094789252</v>
+        <v>0.0114056109963859</v>
       </c>
       <c r="AA9">
-        <v>0.04947294756578603</v>
+        <v>-1.369738822908273</v>
+      </c>
+      <c r="AB9">
+        <v>0.1980796049800176</v>
+      </c>
+      <c r="AC9">
+        <v>-0.03797729495532962</v>
+      </c>
+      <c r="AD9">
+        <v>0.006731878593851083</v>
+      </c>
+      <c r="AE9">
+        <v>0.9627347995796776</v>
+      </c>
+      <c r="AF9">
+        <v>1.006754588620332</v>
+      </c>
+      <c r="AG9">
+        <v>-2.053147716251145</v>
+      </c>
+      <c r="AH9">
+        <v>0.009018500526151949</v>
       </c>
     </row>
     <row r="10">
@@ -2208,64 +2403,84 @@
         </is>
       </c>
       <c r="J10">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="K10">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="L10">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="M10">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="N10">
+        <v>0.1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q10">
         <v>0.2130269863307577</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q10">
+      <c r="X10">
         <v>-0.01650615869253858</v>
       </c>
-      <c r="R10">
+      <c r="Y10">
         <v>0.983629321501455</v>
       </c>
-      <c r="S10">
+      <c r="Z10">
         <v>0.0267672554654336</v>
       </c>
-      <c r="T10">
+      <c r="AA10">
         <v>-0.6166548794609935</v>
       </c>
-      <c r="U10">
+      <c r="AB10">
         <v>0.5456327536525746</v>
       </c>
-      <c r="V10">
+      <c r="AC10">
         <v>-0.06896901536977135</v>
       </c>
-      <c r="W10">
+      <c r="AD10">
         <v>0.03595669798469419</v>
       </c>
-      <c r="X10">
+      <c r="AE10">
         <v>0.9333555993082903</v>
       </c>
-      <c r="Y10">
+      <c r="AF10">
         <v>1.036610958175476</v>
       </c>
-      <c r="Z10">
+      <c r="AG10">
         <v>-0.4058176217004146</v>
       </c>
-      <c r="AA10">
+      <c r="AH10">
         <v>0.2130269863307577</v>
       </c>
     </row>
@@ -2312,64 +2527,84 @@
         </is>
       </c>
       <c r="J11">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="K11">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="L11">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="M11">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="N11">
+        <v>0.1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q11">
         <v>0.3518414027608091</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q11">
+      <c r="X11">
         <v>-0.1514253255935879</v>
       </c>
-      <c r="R11">
+      <c r="Y11">
         <v>0.8594820611893771</v>
       </c>
-      <c r="S11">
+      <c r="Z11">
         <v>0.1500586842514219</v>
       </c>
-      <c r="T11">
+      <c r="AA11">
         <v>-1.009107379216228</v>
       </c>
-      <c r="U11">
+      <c r="AB11">
         <v>0.3238937376980864</v>
       </c>
-      <c r="V11">
+      <c r="AC11">
         <v>-0.4455349422938426</v>
       </c>
-      <c r="W11">
+      <c r="AD11">
         <v>0.1426842911066667</v>
       </c>
-      <c r="X11">
+      <c r="AE11">
         <v>0.6404815636979818</v>
       </c>
-      <c r="Y11">
+      <c r="AF11">
         <v>1.15336561639841</v>
       </c>
-      <c r="Z11">
+      <c r="AG11">
         <v>-1.66112279063935</v>
       </c>
-      <c r="AA11">
+      <c r="AH11">
         <v>0.3518414027608091</v>
       </c>
     </row>
@@ -2380,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2421,22 +2656,57 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -2472,23 +2742,43 @@
       <c r="G2">
         <v>53</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>peese</t>
+        </is>
+      </c>
+      <c r="K2">
+        <v>-0.2280248923827685</v>
+      </c>
+      <c r="L2">
+        <v>0.05623988471185582</v>
+      </c>
+      <c r="M2">
+        <v>-4.054504975446704</v>
+      </c>
+      <c r="N2">
+        <v>5.02405812419616E-05</v>
+      </c>
+      <c r="O2">
+        <v>0.1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R2">
         <v>0.1061267217701378</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -2523,23 +2813,43 @@
       <c r="G3">
         <v>11</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K3">
+        <v>-0.01398931214936958</v>
+      </c>
+      <c r="L3">
+        <v>0.02801957205396191</v>
+      </c>
+      <c r="M3">
+        <v>-0.4992693008454251</v>
+      </c>
+      <c r="N3">
+        <v>0.6175896790784481</v>
+      </c>
+      <c r="O3">
+        <v>0.1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R3">
         <v>0.06140889364563524</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -2574,23 +2884,43 @@
       <c r="G4">
         <v>32</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-0.01300522048704099</v>
+      </c>
+      <c r="L4">
+        <v>0.02317731125588256</v>
+      </c>
+      <c r="M4">
+        <v>-0.5611186018714822</v>
+      </c>
+      <c r="N4">
+        <v>0.5747166878669911</v>
+      </c>
+      <c r="O4">
+        <v>0.1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R4">
         <v>3.648344743013438E-07</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -2625,23 +2955,43 @@
       <c r="G5">
         <v>23</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>peese</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>-0.2071747835899547</v>
+      </c>
+      <c r="L5">
+        <v>0.1133988387623222</v>
+      </c>
+      <c r="M5">
+        <v>-1.826956835282783</v>
+      </c>
+      <c r="N5">
+        <v>0.0677062596835441</v>
+      </c>
+      <c r="O5">
+        <v>0.1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R5">
         <v>0.8755791713346561</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -2676,23 +3026,43 @@
       <c r="G6">
         <v>13</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-0.002326701182641406</v>
+      </c>
+      <c r="L6">
+        <v>0.009419121958906233</v>
+      </c>
+      <c r="M6">
+        <v>-0.2470189039692174</v>
+      </c>
+      <c r="N6">
+        <v>0.8048935940809889</v>
+      </c>
+      <c r="O6">
+        <v>0.1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R6">
         <v>0.05791197033513358</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -2727,23 +3097,43 @@
       <c r="G7">
         <v>13</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>0.01125249478786305</v>
+      </c>
+      <c r="L7">
+        <v>0.01867213013725901</v>
+      </c>
+      <c r="M7">
+        <v>0.6026358377510148</v>
+      </c>
+      <c r="N7">
+        <v>0.5467509738989856</v>
+      </c>
+      <c r="O7">
+        <v>0.1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R7">
         <v>0.001963325122337626</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -2778,23 +3168,43 @@
       <c r="G8">
         <v>28</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="L8">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="M8">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="N8">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="O8">
+        <v>0.1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R8">
         <v>0.6896331316971431</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -2829,23 +3239,43 @@
       <c r="G9">
         <v>12</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>-0.01562270818073927</v>
+      </c>
+      <c r="L9">
+        <v>0.01140561087549029</v>
+      </c>
+      <c r="M9">
+        <v>-1.369738837427039</v>
+      </c>
+      <c r="N9">
+        <v>0.1707684405789152</v>
+      </c>
+      <c r="O9">
+        <v>0.1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R9">
         <v>0.009018500526151949</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -2880,23 +3310,43 @@
       <c r="G10">
         <v>18</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="L10">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="M10">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="N10">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="O10">
+        <v>0.1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R10">
         <v>0.2130269863307577</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -2931,23 +3381,43 @@
       <c r="G11">
         <v>23</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="L11">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="M11">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="N11">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="O11">
+        <v>0.1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R11">
         <v>0.3518414027608091</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
   </sheetData>
